--- a/artfynd/A 20710-2023 artfynd.xlsx
+++ b/artfynd/A 20710-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20710-2023 artfynd.xlsx
+++ b/artfynd/A 20710-2023 artfynd.xlsx
@@ -675,54 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111120130</v>
+        <v>112619543</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oxbacken, Hls</t>
+          <t>Oxbacken SV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567670.5142477506</v>
+        <v>567539</v>
       </c>
       <c r="R2" t="n">
-        <v>6816517.358500944</v>
+        <v>6816611</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,58 +780,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112619543</v>
+        <v>111120130</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oxbacken SV, Hls</t>
+          <t>Oxbacken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567539</v>
+        <v>567671</v>
       </c>
       <c r="R3" t="n">
-        <v>6816611</v>
+        <v>6816517</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20710-2023 artfynd.xlsx
+++ b/artfynd/A 20710-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111120130</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>